--- a/data/preorders.xlsx
+++ b/data/preorders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,12 +489,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1050.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -522,15 +522,19 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1500</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1500.0</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -558,15 +562,19 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>700</v>
-      </c>
-      <c r="F4" t="n">
-        <v>700</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Paid</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -601,12 +609,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>650.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -646,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -681,7 +689,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -691,7 +699,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -719,18 +727,24 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>1600</v>
-      </c>
-      <c r="F8" t="n">
-        <v>400</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1200</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -760,22 +774,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>500.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1500.0</t>
+          <t>1400.0</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Paid</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -803,18 +817,24 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>1700</v>
-      </c>
-      <c r="F10" t="n">
-        <v>500</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1200</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>500.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1200.0</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Paid</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -842,18 +862,24 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F11" t="n">
-        <v>750</v>
-      </c>
-      <c r="G11" t="n">
-        <v>750</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1575</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>750.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>825.0</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -873,7 +899,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jada Nano Metalfigs * 9</t>
+          <t>Jada Nano Metalfigs * 6</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -881,18 +907,24 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>2600</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1300</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1300</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1300.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>400.0</t>
+        </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -920,23 +952,315 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>1580</v>
-      </c>
-      <c r="F13" t="n">
-        <v>100</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1480</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1480.0</t>
+        </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ankush Gowda</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PopRace Skyline GT-R R33 (S42-APAxpo2025)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1700</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>Pending</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2025-12-28</t>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Micro Cars</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mini GT LB Works Lamborghini Murcielago GT EVO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>775.0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>700.0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mini Forge</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MBOX Container Vertical Parking Garage</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>300</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2700</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Mini Wheels</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Hot Wheels Premium Lamborghini Temerario</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>900.0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ankush Gowda</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PopRace RWB 930 Stella Artois (PR640468)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1550</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ankush Gowda</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Mini GT Porsche 911 (992) - Rubystone Red Set [ Porsche 911 GT3 RS, Porsche 911 GT3, Porsche 911 Carrera Coupe, Porsche 911 Targa ]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4900</v>
+      </c>
+      <c r="F19" t="n">
+        <v>400</v>
+      </c>
+      <c r="G19" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rishi Rathod</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HotWheels Premium Ferrari F50</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F20" t="n">
+        <v>750</v>
+      </c>
+      <c r="G20" t="n">
+        <v>750</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
         </is>
       </c>
     </row>

--- a/data/preorders.xlsx
+++ b/data/preorders.xlsx
@@ -997,18 +997,24 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F14" t="n">
-        <v>300</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1700</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Paid</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">

--- a/data/preorders.xlsx
+++ b/data/preorders.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,51 +425,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>S.No</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Seller</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Models</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ETA</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Total Price</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PO Amount</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>On Arrival Amount</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Delivery Status</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Date Added</t>
         </is>
@@ -482,15 +494,11 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1050</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1050.0</t>
-        </is>
+      <c r="E2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1050</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -522,15 +530,11 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1500.0</t>
-        </is>
+      <c r="E3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1500</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -562,15 +566,11 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>700.0</t>
-        </is>
+      <c r="E4" t="n">
+        <v>700</v>
+      </c>
+      <c r="F4" t="n">
+        <v>700</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -602,15 +602,11 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>650.0</t>
-        </is>
+      <c r="E5" t="n">
+        <v>650</v>
+      </c>
+      <c r="F5" t="n">
+        <v>650</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -642,15 +638,11 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1450</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1450.0</t>
-        </is>
+      <c r="E6" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1450</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -682,20 +674,14 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1450</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>200.0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1250.0</t>
-        </is>
+      <c r="E7" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F7" t="n">
+        <v>200</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1250</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -727,20 +713,14 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
+      <c r="E8" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F8" t="n">
+        <v>400</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1200</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -772,24 +752,18 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1900</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
+      <c r="E9" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F9" t="n">
+        <v>500</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1400</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paid</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -817,24 +791,18 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>500.0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1200.0</t>
-        </is>
+      <c r="E10" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F10" t="n">
+        <v>500</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1200</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paid</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -862,20 +830,14 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>1575</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>750.0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>825.0</t>
-        </is>
+      <c r="E11" t="n">
+        <v>1575</v>
+      </c>
+      <c r="F11" t="n">
+        <v>750</v>
+      </c>
+      <c r="G11" t="n">
+        <v>825</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -907,20 +869,14 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1300.0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>400.0</t>
-        </is>
+      <c r="E12" t="n">
+        <v>1700</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1300</v>
+      </c>
+      <c r="G12" t="n">
+        <v>400</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -952,20 +908,14 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1580</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>1480.0</t>
-        </is>
+      <c r="E13" t="n">
+        <v>1580</v>
+      </c>
+      <c r="F13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1480</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -997,24 +947,18 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
+      <c r="E14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1700</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paid</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1042,24 +986,18 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1475</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>775.0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>700.0</t>
-        </is>
+      <c r="E15" t="n">
+        <v>1475</v>
+      </c>
+      <c r="F15" t="n">
+        <v>775</v>
+      </c>
+      <c r="G15" t="n">
+        <v>700</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1098,7 +1036,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Paid</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1126,15 +1064,11 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>900.0</t>
-        </is>
+      <c r="E17" t="n">
+        <v>900</v>
+      </c>
+      <c r="F17" t="n">
+        <v>900</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1166,20 +1100,14 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1550</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>150.0</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
+      <c r="E18" t="n">
+        <v>1550</v>
+      </c>
+      <c r="F18" t="n">
+        <v>150</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1400</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1237,27 +1165,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rishi Rathod</t>
+          <t>Nitin Kumar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HotWheels Premium Ferrari F50</t>
+          <t>PopRace RWB 930 Apple (PR640474)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="F20" t="n">
-        <v>750</v>
+        <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>750</v>
+        <v>1900</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1266,7 +1194,121 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Eterna Toys</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tarmac Works RWB 993 "Furusato"</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F21" t="n">
+        <v>100</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ankush Gowda</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Mini GT 1226 Lamborghini Huracan GT</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Harla Diecast</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Hot Wheels Ferrari 250 GTO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F23" t="n">
+        <v>300</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
         </is>
       </c>
     </row>

--- a/data/preorders.xlsx
+++ b/data/preorders.xlsx
@@ -1279,7 +1279,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Harla Diecast</t>
+          <t>Harla Hotwheels Diecast</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">

--- a/data/preorders.xlsx
+++ b/data/preorders.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1312,6 +1312,45 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>24</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MW Garage</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Blokees Transformers * 12</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
